--- a/results/EReventmodels_summary_organized.xlsx
+++ b/results/EReventmodels_summary_organized.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/awebster2/Library/CloudStorage/Dropbox/UNM/BEGI/BEGI_clean/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B7FC9F0A-46E8-B24D-BE0E-0A855C2E0769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7EA86379-C667-0841-89CF-05B90E5877EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="660" windowWidth="27800" windowHeight="17180" activeTab="2" xr2:uid="{E5BA8005-7531-2F49-B87C-B08CF1A18DE1}"/>
   </bookViews>
